--- a/examples/sample_bill.xlsx
+++ b/examples/sample_bill.xlsx
@@ -501,6 +501,20 @@
       <c r="F2" t="n">
         <v>2399.49</v>
       </c>
+      <c r="G2" t="n">
+        <v>75000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>原清单报价</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/sample_bill.xlsx
+++ b/examples/sample_bill.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="报价清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="报价清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
